--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_7.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02479616152384913</v>
+        <v>0.01962454776149142</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00844575525956528</v>
+        <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>30578656</v>
+        <v>4168090</v>
       </c>
       <c r="L2" t="n">
-        <v>16740357</v>
+        <v>2075075</v>
       </c>
       <c r="M2" t="n">
-        <v>4018279</v>
+        <v>428007</v>
       </c>
       <c r="N2" t="n">
-        <v>178592</v>
+        <v>10753</v>
       </c>
       <c r="O2" t="n">
-        <v>2440238</v>
+        <v>259231</v>
       </c>
       <c r="P2" t="n">
-        <v>969954</v>
+        <v>99614</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999776482582092</v>
+        <v>0.9999932050704956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8592261075973511</v>
+        <v>0.7980192899703979</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7272571325302124</v>
+        <v>0.6274111270904541</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6563674807548523</v>
+        <v>0.5293087363243103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3167872726917267</v>
+        <v>0.1075213998556137</v>
       </c>
       <c r="V2" t="n">
-        <v>0.711402952671051</v>
+        <v>0.5876228809356689</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8037045001983643</v>
+        <v>0.7303133010864258</v>
       </c>
       <c r="X2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44073939</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33537194</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20778128</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5598015</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>412676</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3214748</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562734365463257</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114123582839966</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583261370658875</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6621037125587463</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020463824272156</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006239831905901982</v>
+        <v>0.004824164481952432</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002025556556289107</v>
+        <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>702</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>30578656</v>
+        <v>4168090</v>
       </c>
       <c r="E3" t="n">
-        <v>4316287</v>
+        <v>806781</v>
       </c>
       <c r="F3" t="n">
-        <v>111171</v>
+        <v>21374</v>
       </c>
       <c r="G3" t="n">
-        <v>10313</v>
+        <v>1582</v>
       </c>
       <c r="H3" t="n">
-        <v>6731</v>
+        <v>1259</v>
       </c>
       <c r="I3" t="n">
-        <v>308</v>
+        <v>52</v>
       </c>
       <c r="J3" t="n">
-        <v>69929875</v>
+        <v>10016579</v>
       </c>
       <c r="K3" t="n">
-        <v>73970685</v>
+        <v>10275505</v>
       </c>
       <c r="L3" t="n">
-        <v>84891470</v>
+        <v>11809795</v>
       </c>
       <c r="M3" t="n">
-        <v>105372793</v>
+        <v>15012443</v>
       </c>
       <c r="N3" t="n">
-        <v>112995795</v>
+        <v>16150881</v>
       </c>
       <c r="O3" t="n">
-        <v>109449029</v>
+        <v>15637237</v>
       </c>
       <c r="P3" t="n">
-        <v>112414368</v>
+        <v>16099308</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8730730414390564</v>
+        <v>0.8337612152099609</v>
       </c>
       <c r="S3" t="n">
-        <v>0.733094334602356</v>
+        <v>0.6311978697776794</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6155178546905518</v>
+        <v>0.4570043981075287</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2862799167633057</v>
+        <v>0.1201936006546021</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6843390464782715</v>
+        <v>0.5078559517860413</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7166095972061157</v>
+        <v>0.5147824287414551</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33537194</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1379747</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59295</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47509</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>69930861</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77447110</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89150002</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106552511</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113170359</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110089877</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112558488</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575443267822266</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099165201187134</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575009703636169</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661512553691864</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015421867370605</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0607675802146754</v>
+        <v>0.05054341177459717</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03195414901321388</v>
+        <v>0.03193072151668488</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4702765</v>
+        <v>984168</v>
       </c>
       <c r="E4" t="n">
-        <v>16740357</v>
+        <v>2075075</v>
       </c>
       <c r="F4" t="n">
-        <v>1211005</v>
+        <v>192864</v>
       </c>
       <c r="G4" t="n">
-        <v>53517</v>
+        <v>11035</v>
       </c>
       <c r="H4" t="n">
-        <v>116433</v>
+        <v>22262</v>
       </c>
       <c r="I4" t="n">
-        <v>11074</v>
+        <v>2114</v>
       </c>
       <c r="J4" t="n">
-        <v>986</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>5009947</v>
+        <v>1054954</v>
       </c>
       <c r="L4" t="n">
-        <v>6278128</v>
+        <v>1232286</v>
       </c>
       <c r="M4" t="n">
-        <v>2103717</v>
+        <v>380608</v>
       </c>
       <c r="N4" t="n">
-        <v>385168</v>
+        <v>89255</v>
       </c>
       <c r="O4" t="n">
-        <v>989939</v>
+        <v>181921</v>
       </c>
       <c r="P4" t="n">
-        <v>236900</v>
+        <v>36785</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999988853931427</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8660942316055298</v>
+        <v>0.8154988288879395</v>
       </c>
       <c r="S4" t="n">
-        <v>0.730164110660553</v>
+        <v>0.6292987465858459</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6352866888046265</v>
+        <v>0.4905063509941101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3007619678974152</v>
+        <v>0.1135049015283585</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6976086497306824</v>
+        <v>0.5448353886604309</v>
       </c>
       <c r="W4" t="n">
-        <v>0.757662296295166</v>
+        <v>0.6038932204246521</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1431925</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20778128</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>578265</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38438</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7970</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1533522</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2019596</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>923999</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210604</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349091</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569084644317627</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106638431549072</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579133749008179</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6618080139160156</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017941355705261</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>208982</v>
+        <v>50461</v>
       </c>
       <c r="E5" t="n">
-        <v>1641697</v>
+        <v>349051</v>
       </c>
       <c r="F5" t="n">
-        <v>4018279</v>
+        <v>428007</v>
       </c>
       <c r="G5" t="n">
-        <v>141002</v>
+        <v>26826</v>
       </c>
       <c r="H5" t="n">
-        <v>473496</v>
+        <v>73435</v>
       </c>
       <c r="I5" t="n">
-        <v>44787</v>
+        <v>8756</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4445512</v>
+        <v>831051</v>
       </c>
       <c r="L5" t="n">
-        <v>6094845</v>
+        <v>1212444</v>
       </c>
       <c r="M5" t="n">
-        <v>2510011</v>
+        <v>508542</v>
       </c>
       <c r="N5" t="n">
-        <v>445245</v>
+        <v>78711</v>
       </c>
       <c r="O5" t="n">
-        <v>1125594</v>
+        <v>251211</v>
       </c>
       <c r="P5" t="n">
-        <v>383578</v>
+        <v>93893</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999913573265076</v>
+        <v>0.9999973773956299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9170608520507812</v>
+        <v>0.8845039010047913</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8914697170257568</v>
+        <v>0.850288450717926</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9595304131507874</v>
+        <v>0.9455497860908508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9927159547805786</v>
+        <v>0.9897140264511108</v>
       </c>
       <c r="V5" t="n">
-        <v>0.981443464756012</v>
+        <v>0.9734756350517273</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945574402809143</v>
+        <v>0.9919974803924561</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>55991</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596237</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5598015</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69658</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>203958</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1486974</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2057074</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>930275</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211161</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351084</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735055565834045</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642412662506104</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837351441383362</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963004589080811</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938583970069885</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983702301979065</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>87884</v>
+        <v>17217</v>
       </c>
       <c r="E6" t="n">
-        <v>128270</v>
+        <v>22679</v>
       </c>
       <c r="F6" t="n">
-        <v>148243</v>
+        <v>28016</v>
       </c>
       <c r="G6" t="n">
-        <v>178592</v>
+        <v>10753</v>
       </c>
       <c r="H6" t="n">
-        <v>73231</v>
+        <v>9656</v>
       </c>
       <c r="I6" t="n">
-        <v>7559</v>
+        <v>1138</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45255</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37378</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76298</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>412676</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48863</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>10021</v>
+        <v>3036</v>
       </c>
       <c r="E7" t="n">
-        <v>178335</v>
+        <v>49740</v>
       </c>
       <c r="F7" t="n">
-        <v>598241</v>
+        <v>128801</v>
       </c>
       <c r="G7" t="n">
-        <v>165768</v>
+        <v>44896</v>
       </c>
       <c r="H7" t="n">
-        <v>2440238</v>
+        <v>259231</v>
       </c>
       <c r="I7" t="n">
-        <v>173172</v>
+        <v>24725</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5667</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207826</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53140</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3214748</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>13539</v>
+        <v>4035</v>
       </c>
       <c r="F8" t="n">
-        <v>35057</v>
+        <v>9553</v>
       </c>
       <c r="G8" t="n">
-        <v>14568</v>
+        <v>4916</v>
       </c>
       <c r="H8" t="n">
-        <v>320048</v>
+        <v>75309</v>
       </c>
       <c r="I8" t="n">
-        <v>969954</v>
+        <v>99614</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
